--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.39821</v>
+        <v>16.45266</v>
       </c>
       <c r="D2" t="n">
         <v>16.37973</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45266</v>
+        <v>16.39821</v>
       </c>
       <c r="F2" t="n">
         <v>43.28434</v>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.67758</v>
+        <v>16.80282</v>
       </c>
       <c r="D3" t="n">
         <v>16.39224</v>
       </c>
       <c r="E3" t="n">
-        <v>16.80282</v>
+        <v>16.67758</v>
       </c>
       <c r="F3" t="n">
         <v>42.45828</v>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.61471</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.23744</v>
+      </c>
+      <c r="E4" t="n">
         <v>16.36581</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.61471</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.23744</v>
       </c>
       <c r="F4" t="n">
         <v>42.00926</v>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.28006</v>
+        <v>16.35497</v>
       </c>
       <c r="D6" t="n">
         <v>15.71221</v>
       </c>
       <c r="E6" t="n">
-        <v>16.35497</v>
+        <v>16.28006</v>
       </c>
       <c r="F6" t="n">
         <v>21.60422</v>
